--- a/data/nzd0249/nzd0249.xlsx
+++ b/data/nzd0249/nzd0249.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R429"/>
+  <dimension ref="A1:R430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26174,6 +26174,66 @@
       <c r="R429" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:53:47+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>310.41</v>
+      </c>
+      <c r="C430" t="n">
+        <v>313.73</v>
+      </c>
+      <c r="D430" t="n">
+        <v>315.64</v>
+      </c>
+      <c r="E430" t="n">
+        <v>323.17</v>
+      </c>
+      <c r="F430" t="n">
+        <v>327.11</v>
+      </c>
+      <c r="G430" t="n">
+        <v>332.51</v>
+      </c>
+      <c r="H430" t="n">
+        <v>340.48</v>
+      </c>
+      <c r="I430" t="n">
+        <v>339.89</v>
+      </c>
+      <c r="J430" t="n">
+        <v>337.52</v>
+      </c>
+      <c r="K430" t="n">
+        <v>324.07</v>
+      </c>
+      <c r="L430" t="n">
+        <v>317.23</v>
+      </c>
+      <c r="M430" t="n">
+        <v>317.63</v>
+      </c>
+      <c r="N430" t="n">
+        <v>331.92</v>
+      </c>
+      <c r="O430" t="n">
+        <v>345.63</v>
+      </c>
+      <c r="P430" t="n">
+        <v>332.71</v>
+      </c>
+      <c r="Q430" t="n">
+        <v>319.97</v>
+      </c>
+      <c r="R430" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -26188,7 +26248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B431"/>
+  <dimension ref="A1:B432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30501,6 +30561,16 @@
       </c>
       <c r="B431" t="n">
         <v>-0.11</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>
@@ -30669,28 +30739,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01684356589985621</v>
+        <v>0.01580428901704334</v>
       </c>
       <c r="J2" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K2" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001833940311189997</v>
+        <v>0.0001623726659587543</v>
       </c>
       <c r="M2" t="n">
-        <v>7.279410106519101</v>
+        <v>7.267324560705409</v>
       </c>
       <c r="N2" t="n">
-        <v>85.13860583507966</v>
+        <v>84.94912595009492</v>
       </c>
       <c r="O2" t="n">
-        <v>9.22705835220953</v>
+        <v>9.216785011602198</v>
       </c>
       <c r="P2" t="n">
-        <v>312.0789807169635</v>
+        <v>312.0894615295618</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30747,28 +30817,28 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08005708243022211</v>
+        <v>0.08014763233824886</v>
       </c>
       <c r="J3" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K3" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006348767560292568</v>
+        <v>0.006399386715107203</v>
       </c>
       <c r="M3" t="n">
-        <v>5.878714410008987</v>
+        <v>5.86532480384141</v>
       </c>
       <c r="N3" t="n">
-        <v>55.21630885226973</v>
+        <v>55.08677187061544</v>
       </c>
       <c r="O3" t="n">
-        <v>7.430767716210064</v>
+        <v>7.422046339832124</v>
       </c>
       <c r="P3" t="n">
-        <v>311.4267776483327</v>
+        <v>311.4258644781925</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30825,28 +30895,28 @@
         <v>0.059</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2121630118090179</v>
+        <v>0.211948387765697</v>
       </c>
       <c r="J4" t="n">
+        <v>429</v>
+      </c>
+      <c r="K4" t="n">
         <v>428</v>
       </c>
-      <c r="K4" t="n">
-        <v>427</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.06534174610005206</v>
+        <v>0.06556828440843487</v>
       </c>
       <c r="M4" t="n">
-        <v>4.862709351695786</v>
+        <v>4.852438491386694</v>
       </c>
       <c r="N4" t="n">
-        <v>35.28764722572395</v>
+        <v>35.20563948750631</v>
       </c>
       <c r="O4" t="n">
-        <v>5.940340665797202</v>
+        <v>5.933434038354712</v>
       </c>
       <c r="P4" t="n">
-        <v>310.4618455917565</v>
+        <v>310.4640133118658</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30903,28 +30973,28 @@
         <v>0.09429999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.126325079701991</v>
+        <v>0.1289370638196624</v>
       </c>
       <c r="J5" t="n">
+        <v>429</v>
+      </c>
+      <c r="K5" t="n">
         <v>428</v>
       </c>
-      <c r="K5" t="n">
-        <v>427</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.01517761111126581</v>
+        <v>0.01587326164342373</v>
       </c>
       <c r="M5" t="n">
-        <v>5.953413260674016</v>
+        <v>5.949813661208733</v>
       </c>
       <c r="N5" t="n">
-        <v>56.74856757461349</v>
+        <v>56.68115113773386</v>
       </c>
       <c r="O5" t="n">
-        <v>7.533164512647622</v>
+        <v>7.528688540359062</v>
       </c>
       <c r="P5" t="n">
-        <v>314.5291629240249</v>
+        <v>314.502781674238</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30981,28 +31051,28 @@
         <v>0.0727</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1482856263177613</v>
+        <v>0.1494435252553586</v>
       </c>
       <c r="J6" t="n">
+        <v>429</v>
+      </c>
+      <c r="K6" t="n">
         <v>428</v>
       </c>
-      <c r="K6" t="n">
-        <v>427</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.01795144379191038</v>
+        <v>0.01832726177278288</v>
       </c>
       <c r="M6" t="n">
-        <v>5.973122828675259</v>
+        <v>5.963086368011622</v>
       </c>
       <c r="N6" t="n">
-        <v>65.92542513810739</v>
+        <v>65.78420150949484</v>
       </c>
       <c r="O6" t="n">
-        <v>8.119447341913572</v>
+        <v>8.110746051350322</v>
       </c>
       <c r="P6" t="n">
-        <v>320.8340364690179</v>
+        <v>320.8223415965667</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31059,28 +31129,28 @@
         <v>0.0653</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3281378566080157</v>
+        <v>0.3277790539687913</v>
       </c>
       <c r="J7" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K7" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1034862398921277</v>
+        <v>0.1038122111575203</v>
       </c>
       <c r="M7" t="n">
-        <v>5.353502566882509</v>
+        <v>5.342984921731945</v>
       </c>
       <c r="N7" t="n">
-        <v>51.47993252046628</v>
+        <v>51.3611752612647</v>
       </c>
       <c r="O7" t="n">
-        <v>7.174951743424222</v>
+        <v>7.16667114225738</v>
       </c>
       <c r="P7" t="n">
-        <v>324.5665170728915</v>
+        <v>324.5701218024727</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31137,28 +31207,28 @@
         <v>0.0597</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2883448988080319</v>
+        <v>0.2884542675420773</v>
       </c>
       <c r="J8" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K8" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09907634356488693</v>
+        <v>0.09965594795605082</v>
       </c>
       <c r="M8" t="n">
-        <v>5.030594246560796</v>
+        <v>5.019377547679277</v>
       </c>
       <c r="N8" t="n">
-        <v>41.72472742217586</v>
+        <v>41.62758243709107</v>
       </c>
       <c r="O8" t="n">
-        <v>6.459468044829687</v>
+        <v>6.45194408198731</v>
       </c>
       <c r="P8" t="n">
-        <v>332.6370006336052</v>
+        <v>332.635901854868</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31215,28 +31285,28 @@
         <v>0.0568</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1566386643003704</v>
+        <v>0.1572359419502658</v>
       </c>
       <c r="J9" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K9" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03425972963855128</v>
+        <v>0.03470033480417944</v>
       </c>
       <c r="M9" t="n">
-        <v>4.875707689676615</v>
+        <v>4.866439844051867</v>
       </c>
       <c r="N9" t="n">
-        <v>38.33793385803305</v>
+        <v>38.25161201016189</v>
       </c>
       <c r="O9" t="n">
-        <v>6.191763388408269</v>
+        <v>6.184788760350825</v>
       </c>
       <c r="P9" t="n">
-        <v>334.5331455418662</v>
+        <v>334.5271542627414</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31293,28 +31363,28 @@
         <v>0.0615</v>
       </c>
       <c r="I10" t="n">
-        <v>0.116960253858339</v>
+        <v>0.1185668704812567</v>
       </c>
       <c r="J10" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K10" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01888286565546371</v>
+        <v>0.0194918543158511</v>
       </c>
       <c r="M10" t="n">
-        <v>4.796904682961769</v>
+        <v>4.792762385772505</v>
       </c>
       <c r="N10" t="n">
-        <v>39.3988833394837</v>
+        <v>39.33166770229651</v>
       </c>
       <c r="O10" t="n">
-        <v>6.276852980553528</v>
+        <v>6.271496448400216</v>
       </c>
       <c r="P10" t="n">
-        <v>331.1423361874643</v>
+        <v>331.1262202510379</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31371,28 +31441,28 @@
         <v>0.0587</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0007058793607517076</v>
+        <v>0.001817552498468636</v>
       </c>
       <c r="J11" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K11" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L11" t="n">
-        <v>5.125211289813691e-07</v>
+        <v>3.416734760675055e-06</v>
       </c>
       <c r="M11" t="n">
-        <v>6.03336802288625</v>
+        <v>6.024736417815024</v>
       </c>
       <c r="N11" t="n">
-        <v>53.65372925914082</v>
+        <v>53.54059031639796</v>
       </c>
       <c r="O11" t="n">
-        <v>7.324870596750555</v>
+        <v>7.317143589980858</v>
       </c>
       <c r="P11" t="n">
-        <v>321.7784378023849</v>
+        <v>321.7672693197541</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31449,28 +31519,28 @@
         <v>0.0634</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01987654804178553</v>
+        <v>0.02019820693385368</v>
       </c>
       <c r="J12" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K12" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0003254382713392401</v>
+        <v>0.000337975293756454</v>
       </c>
       <c r="M12" t="n">
-        <v>6.672131643564359</v>
+        <v>6.658185402290745</v>
       </c>
       <c r="N12" t="n">
-        <v>66.97656723675726</v>
+        <v>66.82144333433881</v>
       </c>
       <c r="O12" t="n">
-        <v>8.183921262863986</v>
+        <v>8.174438410945355</v>
       </c>
       <c r="P12" t="n">
-        <v>316.0490225256505</v>
+        <v>316.0457909626783</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31527,28 +31597,28 @@
         <v>0.0605</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.05892379232019479</v>
+        <v>-0.05770082927766666</v>
       </c>
       <c r="J13" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K13" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L13" t="n">
-        <v>0.002046482378924463</v>
+        <v>0.001973512150047263</v>
       </c>
       <c r="M13" t="n">
-        <v>7.878048880991551</v>
+        <v>7.865553251345273</v>
       </c>
       <c r="N13" t="n">
-        <v>93.44038664636248</v>
+        <v>93.23701269177884</v>
       </c>
       <c r="O13" t="n">
-        <v>9.666456778280368</v>
+        <v>9.65593147716878</v>
       </c>
       <c r="P13" t="n">
-        <v>316.6934272565297</v>
+        <v>316.6811406940185</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31605,28 +31675,28 @@
         <v>0.0692</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.01352842099232686</v>
+        <v>-0.009845543010057122</v>
       </c>
       <c r="J14" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K14" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0001303467022319982</v>
+        <v>6.932044397089943e-05</v>
       </c>
       <c r="M14" t="n">
-        <v>6.850215548713047</v>
+        <v>6.850712488754818</v>
       </c>
       <c r="N14" t="n">
-        <v>77.47980187638132</v>
+        <v>77.43011114998551</v>
       </c>
       <c r="O14" t="n">
-        <v>8.802261179741334</v>
+        <v>8.799438115583603</v>
       </c>
       <c r="P14" t="n">
-        <v>324.7499080139601</v>
+        <v>324.7129077866621</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31683,28 +31753,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0436289793239247</v>
+        <v>0.04849321484608196</v>
       </c>
       <c r="J15" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K15" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001196209180679864</v>
+        <v>0.001481997159608506</v>
       </c>
       <c r="M15" t="n">
-        <v>7.363933320727077</v>
+        <v>7.369465845926871</v>
       </c>
       <c r="N15" t="n">
-        <v>87.71504682816008</v>
+        <v>87.73895519680914</v>
       </c>
       <c r="O15" t="n">
-        <v>9.36563114948267</v>
+        <v>9.366907451064581</v>
       </c>
       <c r="P15" t="n">
-        <v>334.5419173112448</v>
+        <v>334.4930485133056</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31761,28 +31831,28 @@
         <v>0.0862</v>
       </c>
       <c r="I16" t="n">
-        <v>0.04058581958343917</v>
+        <v>0.04584206716904957</v>
       </c>
       <c r="J16" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K16" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L16" t="n">
-        <v>0.001019280594832139</v>
+        <v>0.001303567524791993</v>
       </c>
       <c r="M16" t="n">
-        <v>7.409212283324168</v>
+        <v>7.414807351999315</v>
       </c>
       <c r="N16" t="n">
-        <v>89.09696979256618</v>
+        <v>89.15594950850833</v>
       </c>
       <c r="O16" t="n">
-        <v>9.439119121642982</v>
+        <v>9.442242821941635</v>
       </c>
       <c r="P16" t="n">
-        <v>320.8981239979644</v>
+        <v>320.8453168302172</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31839,28 +31909,28 @@
         <v>0.0844</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1419859812029597</v>
+        <v>0.1462987342666114</v>
       </c>
       <c r="J17" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K17" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01385496615633897</v>
+        <v>0.01474692671771971</v>
       </c>
       <c r="M17" t="n">
-        <v>7.045124839508825</v>
+        <v>7.049001735577249</v>
       </c>
       <c r="N17" t="n">
-        <v>79.19125024133706</v>
+        <v>79.18617966342791</v>
       </c>
       <c r="O17" t="n">
-        <v>8.898946580429453</v>
+        <v>8.898661678220378</v>
       </c>
       <c r="P17" t="n">
-        <v>307.410072109728</v>
+        <v>307.3667438093055</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31898,7 +31968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R429"/>
+  <dimension ref="A1:R430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71317,6 +71387,98 @@
         </is>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:53:47+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>-38.20573404257094,178.333777998403</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>-38.20643739893182,178.3338459963836</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>-38.20714165321176,178.33389797415398</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>-38.207842294087754,178.33401380942598</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>-38.20854523181874,178.33408885467188</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>-38.2092341214142,178.33418109120177</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>-38.209927502887844,178.33419873607653</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>-38.210630400701774,178.3341156608579</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>-38.21133267849703,178.33401229969255</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>-38.2120223698945,178.33378408404104</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>-38.212687967938635,178.3335886975459</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>-38.21335729473043,178.33338708953036</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>-38.214068740908985,178.33333544081958</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>-38.21480044488624,178.33326972987172</t>
+        </is>
+      </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>-38.215537913707934,178.3332859916137</t>
+        </is>
+      </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>-38.21626263164537,178.33343139706136</t>
+        </is>
+      </c>
+      <c r="R430" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0249/nzd0249.xlsx
+++ b/data/nzd0249/nzd0249.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R430"/>
+  <dimension ref="A1:R432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26234,6 +26234,126 @@
       <c r="R430" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-27 21:53:44+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>307.06</v>
+      </c>
+      <c r="C431" t="n">
+        <v>311.21</v>
+      </c>
+      <c r="D431" t="n">
+        <v>313.84</v>
+      </c>
+      <c r="E431" t="n">
+        <v>321.94</v>
+      </c>
+      <c r="F431" t="n">
+        <v>326.43</v>
+      </c>
+      <c r="G431" t="n">
+        <v>330.13</v>
+      </c>
+      <c r="H431" t="n">
+        <v>339.4</v>
+      </c>
+      <c r="I431" t="n">
+        <v>339.1</v>
+      </c>
+      <c r="J431" t="n">
+        <v>336.92</v>
+      </c>
+      <c r="K431" t="n">
+        <v>325.61</v>
+      </c>
+      <c r="L431" t="n">
+        <v>317.72</v>
+      </c>
+      <c r="M431" t="n">
+        <v>319.66</v>
+      </c>
+      <c r="N431" t="n">
+        <v>332.55</v>
+      </c>
+      <c r="O431" t="n">
+        <v>346.29</v>
+      </c>
+      <c r="P431" t="n">
+        <v>335.33</v>
+      </c>
+      <c r="Q431" t="n">
+        <v>322.68</v>
+      </c>
+      <c r="R431" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:53:48+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>305.57</v>
+      </c>
+      <c r="C432" t="n">
+        <v>310.4</v>
+      </c>
+      <c r="D432" t="n">
+        <v>314.43</v>
+      </c>
+      <c r="E432" t="n">
+        <v>322.83</v>
+      </c>
+      <c r="F432" t="n">
+        <v>327.07</v>
+      </c>
+      <c r="G432" t="n">
+        <v>330.27</v>
+      </c>
+      <c r="H432" t="n">
+        <v>340.46</v>
+      </c>
+      <c r="I432" t="n">
+        <v>340.95</v>
+      </c>
+      <c r="J432" t="n">
+        <v>339.52</v>
+      </c>
+      <c r="K432" t="n">
+        <v>329.08</v>
+      </c>
+      <c r="L432" t="n">
+        <v>321.62</v>
+      </c>
+      <c r="M432" t="n">
+        <v>322.92</v>
+      </c>
+      <c r="N432" t="n">
+        <v>335.75</v>
+      </c>
+      <c r="O432" t="n">
+        <v>350.35</v>
+      </c>
+      <c r="P432" t="n">
+        <v>340.18</v>
+      </c>
+      <c r="Q432" t="n">
+        <v>326.33</v>
+      </c>
+      <c r="R432" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -26248,7 +26368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B432"/>
+  <dimension ref="A1:B434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30571,6 +30691,26 @@
       </c>
       <c r="B432" t="n">
         <v>0.05</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-01-27 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>0.66</v>
       </c>
     </row>
   </sheetData>
@@ -30739,28 +30879,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01580428901704334</v>
+        <v>0.009761566763614038</v>
       </c>
       <c r="J2" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K2" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001623726659587543</v>
+        <v>6.253088351693137e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>7.267324560705409</v>
+        <v>7.262468501936907</v>
       </c>
       <c r="N2" t="n">
-        <v>84.94912595009492</v>
+        <v>84.73115710550069</v>
       </c>
       <c r="O2" t="n">
-        <v>9.216785011602198</v>
+        <v>9.204952857320926</v>
       </c>
       <c r="P2" t="n">
-        <v>312.0894615295618</v>
+        <v>312.150599964437</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30817,28 +30957,28 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08014763233824886</v>
+        <v>0.07746493398060093</v>
       </c>
       <c r="J3" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K3" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006399386715107203</v>
+        <v>0.006045166325106766</v>
       </c>
       <c r="M3" t="n">
-        <v>5.86532480384141</v>
+        <v>5.851204794193901</v>
       </c>
       <c r="N3" t="n">
-        <v>55.08677187061544</v>
+        <v>54.86488936949519</v>
       </c>
       <c r="O3" t="n">
-        <v>7.422046339832124</v>
+        <v>7.407083729072812</v>
       </c>
       <c r="P3" t="n">
-        <v>311.4258644781925</v>
+        <v>311.4530082029882</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30895,28 +31035,28 @@
         <v>0.059</v>
       </c>
       <c r="I4" t="n">
-        <v>0.211948387765697</v>
+        <v>0.2100470936579275</v>
       </c>
       <c r="J4" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K4" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06556828440843487</v>
+        <v>0.06513602160677401</v>
       </c>
       <c r="M4" t="n">
-        <v>4.852438491386694</v>
+        <v>4.839599074809645</v>
       </c>
       <c r="N4" t="n">
-        <v>35.20563948750631</v>
+        <v>35.05967608353294</v>
       </c>
       <c r="O4" t="n">
-        <v>5.933434038354712</v>
+        <v>5.92112118466874</v>
       </c>
       <c r="P4" t="n">
-        <v>310.4640133118658</v>
+        <v>310.4832719574534</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30973,28 +31113,28 @@
         <v>0.09429999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1289370638196624</v>
+        <v>0.1332913993557021</v>
       </c>
       <c r="J5" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K5" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01587326164342373</v>
+        <v>0.01710941737151861</v>
       </c>
       <c r="M5" t="n">
-        <v>5.949813661208733</v>
+        <v>5.939109767382377</v>
       </c>
       <c r="N5" t="n">
-        <v>56.68115113773386</v>
+        <v>56.50951200088997</v>
       </c>
       <c r="O5" t="n">
-        <v>7.528688540359062</v>
+        <v>7.517280891445388</v>
       </c>
       <c r="P5" t="n">
-        <v>314.502781674238</v>
+        <v>314.4586610443114</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31051,28 +31191,28 @@
         <v>0.0727</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1494435252553586</v>
+        <v>0.1513622034347277</v>
       </c>
       <c r="J6" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K6" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01832726177278288</v>
+        <v>0.01899915925523199</v>
       </c>
       <c r="M6" t="n">
-        <v>5.963086368011622</v>
+        <v>5.941779227017244</v>
       </c>
       <c r="N6" t="n">
-        <v>65.78420150949484</v>
+        <v>65.49636955458698</v>
       </c>
       <c r="O6" t="n">
-        <v>8.110746051350322</v>
+        <v>8.092982735344675</v>
       </c>
       <c r="P6" t="n">
-        <v>320.8223415965667</v>
+        <v>320.8028988613112</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31129,28 +31269,28 @@
         <v>0.0653</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3277790539687913</v>
+        <v>0.3248098019822595</v>
       </c>
       <c r="J7" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K7" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1038122111575203</v>
+        <v>0.1031051187404666</v>
       </c>
       <c r="M7" t="n">
-        <v>5.342984921731945</v>
+        <v>5.334457727156213</v>
       </c>
       <c r="N7" t="n">
-        <v>51.3611752612647</v>
+        <v>51.16567931396337</v>
       </c>
       <c r="O7" t="n">
-        <v>7.16667114225738</v>
+        <v>7.153018895121372</v>
       </c>
       <c r="P7" t="n">
-        <v>324.5701218024727</v>
+        <v>324.6000443900269</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31207,28 +31347,28 @@
         <v>0.0597</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2884542675420773</v>
+        <v>0.288115059551005</v>
       </c>
       <c r="J8" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K8" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09965594795605082</v>
+        <v>0.1004679193860795</v>
       </c>
       <c r="M8" t="n">
-        <v>5.019377547679277</v>
+        <v>4.998539915640889</v>
       </c>
       <c r="N8" t="n">
-        <v>41.62758243709107</v>
+        <v>41.43623988314867</v>
       </c>
       <c r="O8" t="n">
-        <v>6.45194408198731</v>
+        <v>6.437098716281169</v>
       </c>
       <c r="P8" t="n">
-        <v>332.635901854868</v>
+        <v>332.6393134837064</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31285,28 +31425,28 @@
         <v>0.0568</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1572359419502658</v>
+        <v>0.1585305769875571</v>
       </c>
       <c r="J9" t="n">
+        <v>431</v>
+      </c>
+      <c r="K9" t="n">
         <v>429</v>
       </c>
-      <c r="K9" t="n">
-        <v>427</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.03470033480417944</v>
+        <v>0.03563276675117744</v>
       </c>
       <c r="M9" t="n">
-        <v>4.866439844051867</v>
+        <v>4.848343310035985</v>
       </c>
       <c r="N9" t="n">
-        <v>38.25161201016189</v>
+        <v>38.08537356199426</v>
       </c>
       <c r="O9" t="n">
-        <v>6.184788760350825</v>
+        <v>6.17133482821944</v>
       </c>
       <c r="P9" t="n">
-        <v>334.5271542627414</v>
+        <v>334.5141150940501</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31363,28 +31503,28 @@
         <v>0.0615</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1185668704812567</v>
+        <v>0.1224006039387502</v>
       </c>
       <c r="J10" t="n">
+        <v>431</v>
+      </c>
+      <c r="K10" t="n">
         <v>429</v>
       </c>
-      <c r="K10" t="n">
-        <v>427</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.0194918543158511</v>
+        <v>0.02093741638966484</v>
       </c>
       <c r="M10" t="n">
-        <v>4.792762385772505</v>
+        <v>4.787138758606785</v>
       </c>
       <c r="N10" t="n">
-        <v>39.33166770229651</v>
+        <v>39.22777930970761</v>
       </c>
       <c r="O10" t="n">
-        <v>6.271496448400216</v>
+        <v>6.263208387855829</v>
       </c>
       <c r="P10" t="n">
-        <v>331.1262202510379</v>
+        <v>331.0876268118504</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31441,28 +31581,28 @@
         <v>0.0587</v>
       </c>
       <c r="I11" t="n">
-        <v>0.001817552498468636</v>
+        <v>0.007185721529018522</v>
       </c>
       <c r="J11" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K11" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L11" t="n">
-        <v>3.416734760675055e-06</v>
+        <v>5.385954004366589e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>6.024736417815024</v>
+        <v>6.0226968586526</v>
       </c>
       <c r="N11" t="n">
-        <v>53.54059031639796</v>
+        <v>53.44583987882198</v>
       </c>
       <c r="O11" t="n">
-        <v>7.317143589980858</v>
+        <v>7.310666172027141</v>
       </c>
       <c r="P11" t="n">
-        <v>321.7672693197541</v>
+        <v>321.7131475585234</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31519,28 +31659,28 @@
         <v>0.0634</v>
       </c>
       <c r="I12" t="n">
-        <v>0.02019820693385368</v>
+        <v>0.02320337826168875</v>
       </c>
       <c r="J12" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K12" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L12" t="n">
-        <v>0.000337975293756454</v>
+        <v>0.0004506814150674332</v>
       </c>
       <c r="M12" t="n">
-        <v>6.658185402290745</v>
+        <v>6.642162950869802</v>
       </c>
       <c r="N12" t="n">
-        <v>66.82144333433881</v>
+        <v>66.57270297154244</v>
       </c>
       <c r="O12" t="n">
-        <v>8.174438410945355</v>
+        <v>8.15920970263312</v>
       </c>
       <c r="P12" t="n">
-        <v>316.0457909626783</v>
+        <v>316.0154801045509</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31597,28 +31737,28 @@
         <v>0.0605</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.05770082927766666</v>
+        <v>-0.051744579747703</v>
       </c>
       <c r="J13" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K13" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L13" t="n">
-        <v>0.001973512150047263</v>
+        <v>0.001602736079549749</v>
       </c>
       <c r="M13" t="n">
-        <v>7.865553251345273</v>
+        <v>7.857283137907531</v>
       </c>
       <c r="N13" t="n">
-        <v>93.23701269177884</v>
+        <v>92.98871990381647</v>
       </c>
       <c r="O13" t="n">
-        <v>9.65593147716878</v>
+        <v>9.643065897514985</v>
       </c>
       <c r="P13" t="n">
-        <v>316.6811406940185</v>
+        <v>316.621093806131</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31675,28 +31815,28 @@
         <v>0.0692</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.009845543010057122</v>
+        <v>-0.000437222031650689</v>
       </c>
       <c r="J14" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K14" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L14" t="n">
-        <v>6.932044397089943e-05</v>
+        <v>1.374969700318474e-07</v>
       </c>
       <c r="M14" t="n">
-        <v>6.850712488754818</v>
+        <v>6.860698800157889</v>
       </c>
       <c r="N14" t="n">
-        <v>77.43011114998551</v>
+        <v>77.51219963749547</v>
       </c>
       <c r="O14" t="n">
-        <v>8.799438115583603</v>
+        <v>8.804101296412682</v>
       </c>
       <c r="P14" t="n">
-        <v>324.7129077866621</v>
+        <v>324.6180721682745</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31753,28 +31893,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.04849321484608196</v>
+        <v>0.06066117217197965</v>
       </c>
       <c r="J15" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K15" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001481997159608506</v>
+        <v>0.002324052014373468</v>
       </c>
       <c r="M15" t="n">
-        <v>7.369465845926871</v>
+        <v>7.391725044108722</v>
       </c>
       <c r="N15" t="n">
-        <v>87.73895519680914</v>
+        <v>88.06927619566149</v>
       </c>
       <c r="O15" t="n">
-        <v>9.366907451064581</v>
+        <v>9.384523226869945</v>
       </c>
       <c r="P15" t="n">
-        <v>334.4930485133056</v>
+        <v>334.3703964267016</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31831,28 +31971,28 @@
         <v>0.0862</v>
       </c>
       <c r="I16" t="n">
-        <v>0.04584206716904957</v>
+        <v>0.0610692961403333</v>
       </c>
       <c r="J16" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K16" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L16" t="n">
-        <v>0.001303567524791993</v>
+        <v>0.00230763977074222</v>
       </c>
       <c r="M16" t="n">
-        <v>7.414807351999315</v>
+        <v>7.445945256058071</v>
       </c>
       <c r="N16" t="n">
-        <v>89.15594950850833</v>
+        <v>89.89460592269715</v>
       </c>
       <c r="O16" t="n">
-        <v>9.442242821941635</v>
+        <v>9.481276597731824</v>
       </c>
       <c r="P16" t="n">
-        <v>320.8453168302172</v>
+        <v>320.6918289829031</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31909,28 +32049,28 @@
         <v>0.0844</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1462987342666114</v>
+        <v>0.1591625039405605</v>
       </c>
       <c r="J17" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K17" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01474692671771971</v>
+        <v>0.01742569982436182</v>
       </c>
       <c r="M17" t="n">
-        <v>7.049001735577249</v>
+        <v>7.078168873065969</v>
       </c>
       <c r="N17" t="n">
-        <v>79.18617966342791</v>
+        <v>79.63717947843723</v>
       </c>
       <c r="O17" t="n">
-        <v>8.898661678220378</v>
+        <v>8.923966577617669</v>
       </c>
       <c r="P17" t="n">
-        <v>307.3667438093055</v>
+        <v>307.2370821629888</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31968,7 +32108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R430"/>
+  <dimension ref="A1:R432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71479,6 +71619,190 @@
         </is>
       </c>
     </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-27 21:53:44+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>-38.20573619224549,178.3337399352102</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>-38.20643901603162,178.33381736350094</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>-38.20714280830245,178.3338775218998</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>-38.20784308342042,178.3339998335879</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>-38.20854566820655,178.33408112811895</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>-38.20923440078717,178.33415398113297</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>-38.20992705373954,178.3341864460385</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>-38.21063006549432,178.33410667123013</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>-38.21133242390847,178.33400547206054</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>-38.212023388636275,178.33380158044764</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>-38.21268862509877,178.33359421728662</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>-38.213360906052,178.33340975864502</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>-38.21406986165913,178.33334247613246</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>-38.214800403317696,178.33327724882906</t>
+        </is>
+      </c>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>-38.21553126905386,178.33331462782473</t>
+        </is>
+      </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>-38.21625425578727,178.33346038905623</t>
+        </is>
+      </c>
+      <c r="R431" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:53:48+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>-38.20573714836545,178.3337230056098</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>-38.20643953581222,178.33380816007391</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>-38.207142429689775,178.33388422569436</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>-38.20784251227743,178.33400994618623</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>-38.20854525748862,178.33408840016875</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>-38.20923438435364,178.3341555758429</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>-38.2099274945703,178.33419850848324</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>-38.21063085047271,178.33412772289006</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>-38.21133352712266,178.33403505846593</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>-38.21202568410313,178.33384100416964</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>-38.2126938555474,178.3336381499193</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>-38.21336670550467,178.33344616323683</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>-38.21407555435152,178.33337821105766</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>-38.21480014759759,178.33332350180774</t>
+        </is>
+      </c>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>-38.21551896881789,178.33336763758882</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>-38.216242974639336,178.33349943730326</t>
+        </is>
+      </c>
+      <c r="R432" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0249/nzd0249.xlsx
+++ b/data/nzd0249/nzd0249.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R432"/>
+  <dimension ref="A1:R434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26352,6 +26352,126 @@
         <v>326.33</v>
       </c>
       <c r="R432" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:54:03+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>305.68</v>
+      </c>
+      <c r="C433" t="n">
+        <v>311.26</v>
+      </c>
+      <c r="D433" t="n">
+        <v>315.09</v>
+      </c>
+      <c r="E433" t="n">
+        <v>324.53</v>
+      </c>
+      <c r="F433" t="n">
+        <v>329.46</v>
+      </c>
+      <c r="G433" t="n">
+        <v>331.96</v>
+      </c>
+      <c r="H433" t="n">
+        <v>343.5</v>
+      </c>
+      <c r="I433" t="n">
+        <v>345.44</v>
+      </c>
+      <c r="J433" t="n">
+        <v>344.14</v>
+      </c>
+      <c r="K433" t="n">
+        <v>333.49</v>
+      </c>
+      <c r="L433" t="n">
+        <v>328</v>
+      </c>
+      <c r="M433" t="n">
+        <v>329.05</v>
+      </c>
+      <c r="N433" t="n">
+        <v>342.55</v>
+      </c>
+      <c r="O433" t="n">
+        <v>356.28</v>
+      </c>
+      <c r="P433" t="n">
+        <v>345.81</v>
+      </c>
+      <c r="Q433" t="n">
+        <v>332.29</v>
+      </c>
+      <c r="R433" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-08 21:54:09+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>306.6</v>
+      </c>
+      <c r="C434" t="n">
+        <v>311.08</v>
+      </c>
+      <c r="D434" t="n">
+        <v>314.99</v>
+      </c>
+      <c r="E434" t="n">
+        <v>322.91</v>
+      </c>
+      <c r="F434" t="n">
+        <v>327.66</v>
+      </c>
+      <c r="G434" t="n">
+        <v>330.48</v>
+      </c>
+      <c r="H434" t="n">
+        <v>341.29</v>
+      </c>
+      <c r="I434" t="n">
+        <v>344.38</v>
+      </c>
+      <c r="J434" t="n">
+        <v>343.23</v>
+      </c>
+      <c r="K434" t="n">
+        <v>332.09</v>
+      </c>
+      <c r="L434" t="n">
+        <v>328</v>
+      </c>
+      <c r="M434" t="n">
+        <v>329.05</v>
+      </c>
+      <c r="N434" t="n">
+        <v>342.55</v>
+      </c>
+      <c r="O434" t="n">
+        <v>356.28</v>
+      </c>
+      <c r="P434" t="n">
+        <v>345.81</v>
+      </c>
+      <c r="Q434" t="n">
+        <v>332.29</v>
+      </c>
+      <c r="R434" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26368,7 +26488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B434"/>
+  <dimension ref="A1:B436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30711,6 +30831,26 @@
       </c>
       <c r="B434" t="n">
         <v>0.66</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-03-08 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>
@@ -30879,28 +31019,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>0.009761566763614038</v>
+        <v>0.003708104211069467</v>
       </c>
       <c r="J2" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K2" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L2" t="n">
-        <v>6.253088351693137e-05</v>
+        <v>9.106934443781078e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>7.262468501936907</v>
+        <v>7.257823218494374</v>
       </c>
       <c r="N2" t="n">
-        <v>84.73115710550069</v>
+        <v>84.51808481099984</v>
       </c>
       <c r="O2" t="n">
-        <v>9.204952857320926</v>
+        <v>9.193371786836419</v>
       </c>
       <c r="P2" t="n">
-        <v>312.150599964437</v>
+        <v>312.2119984236259</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30957,28 +31097,28 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07746493398060093</v>
+        <v>0.07520807776031815</v>
       </c>
       <c r="J3" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K3" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006045166325106766</v>
+        <v>0.005761986497192173</v>
       </c>
       <c r="M3" t="n">
-        <v>5.851204794193901</v>
+        <v>5.835067027899024</v>
       </c>
       <c r="N3" t="n">
-        <v>54.86488936949519</v>
+        <v>54.63476206416377</v>
       </c>
       <c r="O3" t="n">
-        <v>7.407083729072812</v>
+        <v>7.39153313353622</v>
       </c>
       <c r="P3" t="n">
-        <v>311.4530082029882</v>
+        <v>311.4758999717101</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31035,28 +31175,28 @@
         <v>0.059</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2100470936579275</v>
+        <v>0.2090573449285801</v>
       </c>
       <c r="J4" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K4" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06513602160677401</v>
+        <v>0.06524335757933153</v>
       </c>
       <c r="M4" t="n">
-        <v>4.839599074809645</v>
+        <v>4.82220633718802</v>
       </c>
       <c r="N4" t="n">
-        <v>35.05967608353294</v>
+        <v>34.90215917551449</v>
       </c>
       <c r="O4" t="n">
-        <v>5.92112118466874</v>
+        <v>5.907804937158512</v>
       </c>
       <c r="P4" t="n">
-        <v>310.4832719574534</v>
+        <v>310.4933260928455</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31113,28 +31253,28 @@
         <v>0.09429999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1332913993557021</v>
+        <v>0.1388129718387872</v>
       </c>
       <c r="J5" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K5" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01710941737151861</v>
+        <v>0.01868738050117436</v>
       </c>
       <c r="M5" t="n">
-        <v>5.939109767382377</v>
+        <v>5.933530411238688</v>
       </c>
       <c r="N5" t="n">
-        <v>56.50951200088997</v>
+        <v>56.39988731022765</v>
       </c>
       <c r="O5" t="n">
-        <v>7.517280891445388</v>
+        <v>7.509985839549077</v>
       </c>
       <c r="P5" t="n">
-        <v>314.4586610443114</v>
+        <v>314.402576135112</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31191,28 +31331,28 @@
         <v>0.0727</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1513622034347277</v>
+        <v>0.1549705881521038</v>
       </c>
       <c r="J6" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K6" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01899915925523199</v>
+        <v>0.02009966591454004</v>
       </c>
       <c r="M6" t="n">
-        <v>5.941779227017244</v>
+        <v>5.92642380820074</v>
       </c>
       <c r="N6" t="n">
-        <v>65.49636955458698</v>
+        <v>65.26056150879565</v>
       </c>
       <c r="O6" t="n">
-        <v>8.092982735344675</v>
+        <v>8.078400925232398</v>
       </c>
       <c r="P6" t="n">
-        <v>320.8028988613112</v>
+        <v>320.7662486366866</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31269,28 +31409,28 @@
         <v>0.0653</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3248098019822595</v>
+        <v>0.3228785325863155</v>
       </c>
       <c r="J7" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K7" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1031051187404666</v>
+        <v>0.1030098221055423</v>
       </c>
       <c r="M7" t="n">
-        <v>5.334457727156213</v>
+        <v>5.320306555564787</v>
       </c>
       <c r="N7" t="n">
-        <v>51.16567931396337</v>
+        <v>50.95029841614954</v>
       </c>
       <c r="O7" t="n">
-        <v>7.153018895121372</v>
+        <v>7.137947773425464</v>
       </c>
       <c r="P7" t="n">
-        <v>324.6000443900269</v>
+        <v>324.6195622902083</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31347,28 +31487,28 @@
         <v>0.0597</v>
       </c>
       <c r="I8" t="n">
-        <v>0.288115059551005</v>
+        <v>0.2901260400477465</v>
       </c>
       <c r="J8" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K8" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1004679193860795</v>
+        <v>0.1027127529779325</v>
       </c>
       <c r="M8" t="n">
-        <v>4.998539915640889</v>
+        <v>4.984773420793137</v>
       </c>
       <c r="N8" t="n">
-        <v>41.43623988314867</v>
+        <v>41.27051481436224</v>
       </c>
       <c r="O8" t="n">
-        <v>6.437098716281169</v>
+        <v>6.424213166945991</v>
       </c>
       <c r="P8" t="n">
-        <v>332.6393134837064</v>
+        <v>332.6189981747277</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31425,28 +31565,28 @@
         <v>0.0568</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1585305769875571</v>
+        <v>0.1644598934257423</v>
       </c>
       <c r="J9" t="n">
+        <v>433</v>
+      </c>
+      <c r="K9" t="n">
         <v>431</v>
       </c>
-      <c r="K9" t="n">
-        <v>429</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.03563276675117744</v>
+        <v>0.03849015878958895</v>
       </c>
       <c r="M9" t="n">
-        <v>4.848343310035985</v>
+        <v>4.847235950171225</v>
       </c>
       <c r="N9" t="n">
-        <v>38.08537356199426</v>
+        <v>38.08447176496213</v>
       </c>
       <c r="O9" t="n">
-        <v>6.17133482821944</v>
+        <v>6.17126176441756</v>
       </c>
       <c r="P9" t="n">
-        <v>334.5141150940501</v>
+        <v>334.4542944484723</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31503,28 +31643,28 @@
         <v>0.0615</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1224006039387502</v>
+        <v>0.1313628819193176</v>
       </c>
       <c r="J10" t="n">
+        <v>433</v>
+      </c>
+      <c r="K10" t="n">
         <v>431</v>
       </c>
-      <c r="K10" t="n">
-        <v>429</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.02093741638966484</v>
+        <v>0.02406543259428728</v>
       </c>
       <c r="M10" t="n">
-        <v>4.787138758606785</v>
+        <v>4.805452245129708</v>
       </c>
       <c r="N10" t="n">
-        <v>39.22777930970761</v>
+        <v>39.44539049897676</v>
       </c>
       <c r="O10" t="n">
-        <v>6.263208387855829</v>
+        <v>6.280556543728968</v>
       </c>
       <c r="P10" t="n">
-        <v>331.0876268118504</v>
+        <v>330.9972052104877</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31581,28 +31721,28 @@
         <v>0.0587</v>
       </c>
       <c r="I11" t="n">
-        <v>0.007185721529018522</v>
+        <v>0.01763072351673596</v>
       </c>
       <c r="J11" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K11" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L11" t="n">
-        <v>5.385954004366589e-05</v>
+        <v>0.0003245361321403406</v>
       </c>
       <c r="M11" t="n">
-        <v>6.0226968586526</v>
+        <v>6.04538350417564</v>
       </c>
       <c r="N11" t="n">
-        <v>53.44583987882198</v>
+        <v>53.73974321689195</v>
       </c>
       <c r="O11" t="n">
-        <v>7.310666172027141</v>
+        <v>7.33073960913167</v>
       </c>
       <c r="P11" t="n">
-        <v>321.7131475585234</v>
+        <v>321.6076081782736</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31659,28 +31799,28 @@
         <v>0.0634</v>
       </c>
       <c r="I12" t="n">
-        <v>0.02320337826168875</v>
+        <v>0.03410844266174025</v>
       </c>
       <c r="J12" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K12" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0004506814150674332</v>
+        <v>0.0009757617836596566</v>
       </c>
       <c r="M12" t="n">
-        <v>6.642162950869802</v>
+        <v>6.665406112286362</v>
       </c>
       <c r="N12" t="n">
-        <v>66.57270297154244</v>
+        <v>66.85214428990078</v>
       </c>
       <c r="O12" t="n">
-        <v>8.15920970263312</v>
+        <v>8.176316058586579</v>
       </c>
       <c r="P12" t="n">
-        <v>316.0154801045509</v>
+        <v>315.9052889632463</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31737,28 +31877,28 @@
         <v>0.0605</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.051744579747703</v>
+        <v>-0.03849917347347732</v>
       </c>
       <c r="J13" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K13" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L13" t="n">
-        <v>0.001602736079549749</v>
+        <v>0.0008896353235989807</v>
       </c>
       <c r="M13" t="n">
-        <v>7.857283137907531</v>
+        <v>7.883884244562566</v>
       </c>
       <c r="N13" t="n">
-        <v>92.98871990381647</v>
+        <v>93.42510564458924</v>
       </c>
       <c r="O13" t="n">
-        <v>9.643065897514985</v>
+        <v>9.665666332156787</v>
       </c>
       <c r="P13" t="n">
-        <v>316.621093806131</v>
+        <v>316.4872544795333</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31815,28 +31955,28 @@
         <v>0.0692</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.000437222031650689</v>
+        <v>0.01678510018269064</v>
       </c>
       <c r="J14" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K14" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L14" t="n">
-        <v>1.374969700318474e-07</v>
+        <v>0.0002010931793557935</v>
       </c>
       <c r="M14" t="n">
-        <v>6.860698800157889</v>
+        <v>6.905359513913194</v>
       </c>
       <c r="N14" t="n">
-        <v>77.51219963749547</v>
+        <v>78.61809795638676</v>
       </c>
       <c r="O14" t="n">
-        <v>8.804101296412682</v>
+        <v>8.866684721833002</v>
       </c>
       <c r="P14" t="n">
-        <v>324.6180721682745</v>
+        <v>324.4440477617871</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31893,28 +32033,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06066117217197965</v>
+        <v>0.08013601737046019</v>
       </c>
       <c r="J15" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K15" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L15" t="n">
-        <v>0.002324052014373468</v>
+        <v>0.004009407588219438</v>
       </c>
       <c r="M15" t="n">
-        <v>7.391725044108722</v>
+        <v>7.448592941260717</v>
       </c>
       <c r="N15" t="n">
-        <v>88.06927619566149</v>
+        <v>89.53438982327026</v>
       </c>
       <c r="O15" t="n">
-        <v>9.384523226869945</v>
+        <v>9.462261348286162</v>
       </c>
       <c r="P15" t="n">
-        <v>334.3703964267016</v>
+        <v>334.1736112147604</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31971,28 +32111,28 @@
         <v>0.0862</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0610692961403333</v>
+        <v>0.08362264355398905</v>
       </c>
       <c r="J16" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K16" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L16" t="n">
-        <v>0.00230763977074222</v>
+        <v>0.004248329320786448</v>
       </c>
       <c r="M16" t="n">
-        <v>7.445945256058071</v>
+        <v>7.510199151481912</v>
       </c>
       <c r="N16" t="n">
-        <v>89.89460592269715</v>
+        <v>91.98986773354073</v>
       </c>
       <c r="O16" t="n">
-        <v>9.481276597731824</v>
+        <v>9.591134851181101</v>
       </c>
       <c r="P16" t="n">
-        <v>320.6918289829031</v>
+        <v>320.4639367858643</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32049,28 +32189,28 @@
         <v>0.0844</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1591625039405605</v>
+        <v>0.1791414315734963</v>
       </c>
       <c r="J17" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K17" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01742569982436182</v>
+        <v>0.02169008125409266</v>
       </c>
       <c r="M17" t="n">
-        <v>7.078168873065969</v>
+        <v>7.142157218136171</v>
       </c>
       <c r="N17" t="n">
-        <v>79.63717947843723</v>
+        <v>81.239398422321</v>
       </c>
       <c r="O17" t="n">
-        <v>8.923966577617669</v>
+        <v>9.013290099753863</v>
       </c>
       <c r="P17" t="n">
-        <v>307.2370821629888</v>
+        <v>307.0352034122792</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32108,7 +32248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R432"/>
+  <dimension ref="A1:R434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71803,6 +71943,190 @@
         </is>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:54:03+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>-38.20573707777949,178.33372425544613</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>-38.20643898394638,178.3338179316137</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>-38.20714200615652,178.33389172485423</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>-38.207841421327764,178.33402926238463</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>-38.20854372370995,178.33411555672848</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>-38.209234185975745,178.33417482627</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>-38.20992875883266,178.33423310266443</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>-38.21063275562054,178.3341788158377</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>-38.211335487430766,178.3340876312325</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>-38.21202860137728,178.333891107518</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>-38.21270241198826,178.33371001920995</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>-38.21337761057854,178.33351461728208</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>-38.21408765128515,178.3334541477882</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>-38.21479977406216,178.33339105849382</t>
+        </is>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>-38.2155046903711,178.33342917260885</t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>-38.21622455388941,178.3335631982476</t>
+        </is>
+      </c>
+      <c r="R433" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-08 21:54:09+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>-38.205736487423714,178.33373470862225</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>-38.20643909945326,178.33381588640773</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>-38.20714207032825,178.3338905886179</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>-38.207842460938714,178.33401085518383</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>-38.20854487885764,178.33409510408953</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>-38.2092343597033,178.33415796790783</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>-38.20992783974822,178.3342079536051</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>-38.210632305854936,178.3341667538055</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>-38.211335101311356,178.33407727599058</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>-38.21202767526086,178.33387520169296</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>-38.21270241198826,178.33371001920995</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>-38.21337761057854,178.33351461728208</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>-38.21408765128515,178.3334541477882</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>-38.21479977406216,178.33339105849382</t>
+        </is>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>-38.2155046903711,178.33342917260885</t>
+        </is>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>-38.21622455388941,178.3335631982476</t>
+        </is>
+      </c>
+      <c r="R434" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0249/nzd0249.xlsx
+++ b/data/nzd0249/nzd0249.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R434"/>
+  <dimension ref="A1:R436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26472,6 +26472,126 @@
         <v>332.29</v>
       </c>
       <c r="R434" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-16 21:53:28+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>306.96</v>
+      </c>
+      <c r="C435" t="n">
+        <v>311.11</v>
+      </c>
+      <c r="D435" t="n">
+        <v>314.61</v>
+      </c>
+      <c r="E435" t="n">
+        <v>321.4</v>
+      </c>
+      <c r="F435" t="n">
+        <v>326.67</v>
+      </c>
+      <c r="G435" t="n">
+        <v>329.86</v>
+      </c>
+      <c r="H435" t="n">
+        <v>340.53</v>
+      </c>
+      <c r="I435" t="n">
+        <v>343.62</v>
+      </c>
+      <c r="J435" t="n">
+        <v>341.94</v>
+      </c>
+      <c r="K435" t="n">
+        <v>331.96</v>
+      </c>
+      <c r="L435" t="n">
+        <v>326.9</v>
+      </c>
+      <c r="M435" t="n">
+        <v>327.49</v>
+      </c>
+      <c r="N435" t="n">
+        <v>341.62</v>
+      </c>
+      <c r="O435" t="n">
+        <v>354.84</v>
+      </c>
+      <c r="P435" t="n">
+        <v>343.99</v>
+      </c>
+      <c r="Q435" t="n">
+        <v>330.05</v>
+      </c>
+      <c r="R435" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:53:48+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>306.3</v>
+      </c>
+      <c r="C436" t="n">
+        <v>307.74</v>
+      </c>
+      <c r="D436" t="n">
+        <v>313.26</v>
+      </c>
+      <c r="E436" t="n">
+        <v>318.21</v>
+      </c>
+      <c r="F436" t="n">
+        <v>322.33</v>
+      </c>
+      <c r="G436" t="n">
+        <v>324.43</v>
+      </c>
+      <c r="H436" t="n">
+        <v>335.64</v>
+      </c>
+      <c r="I436" t="n">
+        <v>340.18</v>
+      </c>
+      <c r="J436" t="n">
+        <v>338.89</v>
+      </c>
+      <c r="K436" t="n">
+        <v>330.75</v>
+      </c>
+      <c r="L436" t="n">
+        <v>324.98</v>
+      </c>
+      <c r="M436" t="n">
+        <v>327.17</v>
+      </c>
+      <c r="N436" t="n">
+        <v>341.41</v>
+      </c>
+      <c r="O436" t="n">
+        <v>356.19</v>
+      </c>
+      <c r="P436" t="n">
+        <v>344.98</v>
+      </c>
+      <c r="Q436" t="n">
+        <v>329.19</v>
+      </c>
+      <c r="R436" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26488,7 +26608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B436"/>
+  <dimension ref="A1:B438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30851,6 +30971,26 @@
       </c>
       <c r="B436" t="n">
         <v>0.61</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-03-16 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>-0.27</v>
       </c>
     </row>
   </sheetData>
@@ -31019,28 +31159,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003708104211069467</v>
+        <v>-0.001729997660638269</v>
       </c>
       <c r="J2" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="K2" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L2" t="n">
-        <v>9.106934443781078e-06</v>
+        <v>2.001222368042122e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>7.257823218494374</v>
+        <v>7.250102212825396</v>
       </c>
       <c r="N2" t="n">
-        <v>84.51808481099984</v>
+        <v>84.27428025602768</v>
       </c>
       <c r="O2" t="n">
-        <v>9.193371786836419</v>
+        <v>9.180102409887795</v>
       </c>
       <c r="P2" t="n">
-        <v>312.2119984236259</v>
+        <v>312.2673605248518</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31097,28 +31237,28 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07520807776031815</v>
+        <v>0.07131970292764381</v>
       </c>
       <c r="J3" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="K3" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005761986497192173</v>
+        <v>0.005234592956678052</v>
       </c>
       <c r="M3" t="n">
-        <v>5.835067027899024</v>
+        <v>5.826895976142956</v>
       </c>
       <c r="N3" t="n">
-        <v>54.63476206416377</v>
+        <v>54.46995880457965</v>
       </c>
       <c r="O3" t="n">
-        <v>7.39153313353622</v>
+        <v>7.380376603167324</v>
       </c>
       <c r="P3" t="n">
-        <v>311.4758999717101</v>
+        <v>311.5155169200516</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31175,28 +31315,28 @@
         <v>0.059</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2090573449285801</v>
+        <v>0.2070149741226192</v>
       </c>
       <c r="J4" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="K4" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06524335757933153</v>
+        <v>0.06469622658872309</v>
       </c>
       <c r="M4" t="n">
-        <v>4.82220633718802</v>
+        <v>4.810192979253646</v>
       </c>
       <c r="N4" t="n">
-        <v>34.90215917551449</v>
+        <v>34.76404930591296</v>
       </c>
       <c r="O4" t="n">
-        <v>5.907804937158512</v>
+        <v>5.896104587429988</v>
       </c>
       <c r="P4" t="n">
-        <v>310.4933260928455</v>
+        <v>310.5141606525762</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31253,28 +31393,28 @@
         <v>0.09429999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1388129718387872</v>
+        <v>0.1404327161386431</v>
       </c>
       <c r="J5" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="K5" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01868738050117436</v>
+        <v>0.01932195947845849</v>
       </c>
       <c r="M5" t="n">
-        <v>5.933530411238688</v>
+        <v>5.912723777836042</v>
       </c>
       <c r="N5" t="n">
-        <v>56.39988731022765</v>
+        <v>56.16489815003095</v>
       </c>
       <c r="O5" t="n">
-        <v>7.509985839549077</v>
+        <v>7.494324395836555</v>
       </c>
       <c r="P5" t="n">
-        <v>314.402576135112</v>
+        <v>314.3860992834647</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31331,28 +31471,28 @@
         <v>0.0727</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1549705881521038</v>
+        <v>0.1545776740389251</v>
       </c>
       <c r="J6" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="K6" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02009966591454004</v>
+        <v>0.02021534881401588</v>
       </c>
       <c r="M6" t="n">
-        <v>5.92642380820074</v>
+        <v>5.909713423000301</v>
       </c>
       <c r="N6" t="n">
-        <v>65.26056150879565</v>
+        <v>64.98244218699155</v>
       </c>
       <c r="O6" t="n">
-        <v>8.078400925232398</v>
+        <v>8.06116878541763</v>
       </c>
       <c r="P6" t="n">
-        <v>320.7662486366866</v>
+        <v>320.7703011345554</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31409,28 +31549,28 @@
         <v>0.0653</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3228785325863155</v>
+        <v>0.3170743031957979</v>
       </c>
       <c r="J7" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="K7" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1030098221055423</v>
+        <v>0.1003603196046333</v>
       </c>
       <c r="M7" t="n">
-        <v>5.320306555564787</v>
+        <v>5.327233314979018</v>
       </c>
       <c r="N7" t="n">
-        <v>50.95029841614954</v>
+        <v>50.91788800939638</v>
       </c>
       <c r="O7" t="n">
-        <v>7.137947773425464</v>
+        <v>7.135677123398758</v>
       </c>
       <c r="P7" t="n">
-        <v>324.6195622902083</v>
+        <v>324.6784786540395</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31487,28 +31627,28 @@
         <v>0.0597</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2901260400477465</v>
+        <v>0.2879516296277057</v>
       </c>
       <c r="J8" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="K8" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1027127529779325</v>
+        <v>0.1022484935337651</v>
       </c>
       <c r="M8" t="n">
-        <v>4.984773420793137</v>
+        <v>4.973568059653294</v>
       </c>
       <c r="N8" t="n">
-        <v>41.27051481436224</v>
+        <v>41.13201893512618</v>
       </c>
       <c r="O8" t="n">
-        <v>6.424213166945991</v>
+        <v>6.413424899001015</v>
       </c>
       <c r="P8" t="n">
-        <v>332.6189981747277</v>
+        <v>332.6411007214358</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31565,28 +31705,28 @@
         <v>0.0568</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1644598934257423</v>
+        <v>0.1673620088310508</v>
       </c>
       <c r="J9" t="n">
+        <v>435</v>
+      </c>
+      <c r="K9" t="n">
         <v>433</v>
       </c>
-      <c r="K9" t="n">
-        <v>431</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.03849015878958895</v>
+        <v>0.04018022279092781</v>
       </c>
       <c r="M9" t="n">
-        <v>4.847235950171225</v>
+        <v>4.835292171400609</v>
       </c>
       <c r="N9" t="n">
-        <v>38.08447176496213</v>
+        <v>37.9648703082408</v>
       </c>
       <c r="O9" t="n">
-        <v>6.17126176441756</v>
+        <v>6.161563949862145</v>
       </c>
       <c r="P9" t="n">
-        <v>334.4542944484723</v>
+        <v>334.4249465858498</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31643,28 +31783,28 @@
         <v>0.0615</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1313628819193176</v>
+        <v>0.1369820445491706</v>
       </c>
       <c r="J10" t="n">
+        <v>435</v>
+      </c>
+      <c r="K10" t="n">
         <v>433</v>
       </c>
-      <c r="K10" t="n">
-        <v>431</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.02406543259428728</v>
+        <v>0.02628982142315384</v>
       </c>
       <c r="M10" t="n">
-        <v>4.805452245129708</v>
+        <v>4.809234596792265</v>
       </c>
       <c r="N10" t="n">
-        <v>39.44539049897676</v>
+        <v>39.43303176287553</v>
       </c>
       <c r="O10" t="n">
-        <v>6.280556543728968</v>
+        <v>6.279572578040287</v>
       </c>
       <c r="P10" t="n">
-        <v>330.9972052104877</v>
+        <v>330.9403417704066</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31721,28 +31861,28 @@
         <v>0.0587</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01763072351673596</v>
+        <v>0.0264585326746369</v>
       </c>
       <c r="J11" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="K11" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0003245361321403406</v>
+        <v>0.000733491631084382</v>
       </c>
       <c r="M11" t="n">
-        <v>6.04538350417564</v>
+        <v>6.060465166730181</v>
       </c>
       <c r="N11" t="n">
-        <v>53.73974321689195</v>
+        <v>53.88394710077539</v>
       </c>
       <c r="O11" t="n">
-        <v>7.33073960913167</v>
+        <v>7.340568581572914</v>
       </c>
       <c r="P11" t="n">
-        <v>321.6076081782736</v>
+        <v>321.5181030797071</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31799,28 +31939,28 @@
         <v>0.0634</v>
       </c>
       <c r="I12" t="n">
-        <v>0.03410844266174025</v>
+        <v>0.04278601981471164</v>
       </c>
       <c r="J12" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="K12" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0009757617836596566</v>
+        <v>0.00154305890034534</v>
       </c>
       <c r="M12" t="n">
-        <v>6.665406112286362</v>
+        <v>6.677401310942303</v>
       </c>
       <c r="N12" t="n">
-        <v>66.85214428990078</v>
+        <v>66.92560928495691</v>
       </c>
       <c r="O12" t="n">
-        <v>8.176316058586579</v>
+        <v>8.180807373661654</v>
       </c>
       <c r="P12" t="n">
-        <v>315.9052889632463</v>
+        <v>315.817314918506</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31877,28 +32017,28 @@
         <v>0.0605</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.03849917347347732</v>
+        <v>-0.02720492547012166</v>
       </c>
       <c r="J13" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="K13" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0008896353235989807</v>
+        <v>0.0004463891199941727</v>
       </c>
       <c r="M13" t="n">
-        <v>7.883884244562566</v>
+        <v>7.900695080300229</v>
       </c>
       <c r="N13" t="n">
-        <v>93.42510564458924</v>
+        <v>93.633076590847</v>
       </c>
       <c r="O13" t="n">
-        <v>9.665666332156787</v>
+        <v>9.676418582866649</v>
       </c>
       <c r="P13" t="n">
-        <v>316.4872544795333</v>
+        <v>316.3727289147178</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31955,28 +32095,28 @@
         <v>0.0692</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01678510018269064</v>
+        <v>0.0326039031715686</v>
       </c>
       <c r="J14" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="K14" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0002010931793557935</v>
+        <v>0.0007548274827403612</v>
       </c>
       <c r="M14" t="n">
-        <v>6.905359513913194</v>
+        <v>6.946307793568896</v>
       </c>
       <c r="N14" t="n">
-        <v>78.61809795638676</v>
+        <v>79.50698141177853</v>
       </c>
       <c r="O14" t="n">
-        <v>8.866684721833002</v>
+        <v>8.916668739601047</v>
       </c>
       <c r="P14" t="n">
-        <v>324.4440477617871</v>
+        <v>324.2836399313517</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32033,28 +32173,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.08013601737046019</v>
+        <v>0.09841983768837972</v>
       </c>
       <c r="J15" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="K15" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L15" t="n">
-        <v>0.004009407588219438</v>
+        <v>0.005991529662255801</v>
       </c>
       <c r="M15" t="n">
-        <v>7.448592941260717</v>
+        <v>7.499725236324117</v>
       </c>
       <c r="N15" t="n">
-        <v>89.53438982327026</v>
+        <v>90.7944666052091</v>
       </c>
       <c r="O15" t="n">
-        <v>9.462261348286162</v>
+        <v>9.528613047301748</v>
       </c>
       <c r="P15" t="n">
-        <v>334.1736112147604</v>
+        <v>333.9881902393545</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32111,28 +32251,28 @@
         <v>0.0862</v>
       </c>
       <c r="I16" t="n">
-        <v>0.08362264355398905</v>
+        <v>0.1043647624283057</v>
       </c>
       <c r="J16" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="K16" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L16" t="n">
-        <v>0.004248329320786448</v>
+        <v>0.006523611906771309</v>
       </c>
       <c r="M16" t="n">
-        <v>7.510199151481912</v>
+        <v>7.566805267914352</v>
       </c>
       <c r="N16" t="n">
-        <v>91.98986773354073</v>
+        <v>93.71711955045544</v>
       </c>
       <c r="O16" t="n">
-        <v>9.591134851181101</v>
+        <v>9.680760277501733</v>
       </c>
       <c r="P16" t="n">
-        <v>320.4639367858643</v>
+        <v>320.2535913225785</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32189,28 +32329,28 @@
         <v>0.0844</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1791414315734963</v>
+        <v>0.1960895305379514</v>
       </c>
       <c r="J17" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="K17" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02169008125409266</v>
+        <v>0.02571722341209748</v>
       </c>
       <c r="M17" t="n">
-        <v>7.142157218136171</v>
+        <v>7.190516089936043</v>
       </c>
       <c r="N17" t="n">
-        <v>81.239398422321</v>
+        <v>82.30220715529467</v>
       </c>
       <c r="O17" t="n">
-        <v>9.013290099753863</v>
+        <v>9.072056390658883</v>
       </c>
       <c r="P17" t="n">
-        <v>307.0352034122792</v>
+        <v>306.8633511864441</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32248,7 +32388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R434"/>
+  <dimension ref="A1:R436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72127,6 +72267,190 @@
         </is>
       </c>
     </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-16 21:53:28+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>-38.20573625641468,178.33373879899543</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>-38.20643908020211,178.33381622727538</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>-38.207142314180764,178.3338862709198</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>-38.207843429956185,178.3339936978539</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>-38.20854551418738,178.33408385513766</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>-38.209234432480336,178.33415090562087</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>-38.20992752368171,178.3341993050598</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>-38.21063198338071,178.334158105556</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>-38.2113345539537,178.33406259658173</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>-38.212027589264224,178.3338737247235</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>-38.2127009367431,178.3336976279521</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>-38.2133748353924,178.33349719667524</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>-38.21408599685461,178.3334437623224</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>-38.214799864772495,178.33337465349803</t>
+        </is>
+      </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>-38.21550930614234,178.33340928029634</t>
+        </is>
+      </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>-38.2162314771281,178.33353923440694</t>
+        </is>
+      </c>
+      <c r="R435" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:53:48+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>-38.205736679931135,178.33373129997787</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>-38.20644124274104,178.33377793647256</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>-38.207143180497575,178.3338709317288</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>-38.20784547707767,178.3339574515717</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>-38.20854829935761,178.33403454154683</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>-38.20923506984813,178.3340890536534</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>-38.20992549002786,178.3341436584986</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>-38.21063052375244,178.3341189608478</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>-38.21133325980607,178.33402788945233</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>-38.21202678883311,178.33385997754627</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>-38.212698361766435,178.3336759995756</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>-38.21337426612312,178.33349362321758</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>-38.214085623273384,178.33344141721727</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>-38.21479977973163,178.3333900331816</t>
+        </is>
+      </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>-38.21550679536607,178.3334201008403</t>
+        </is>
+      </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>-38.216234135156014,178.33353003400248</t>
+        </is>
+      </c>
+      <c r="R436" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0249/nzd0249.xlsx
+++ b/data/nzd0249/nzd0249.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R436"/>
+  <dimension ref="A1:R440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26592,6 +26592,246 @@
         <v>329.19</v>
       </c>
       <c r="R436" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:53:28+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>305.97</v>
+      </c>
+      <c r="C437" t="n">
+        <v>308.34</v>
+      </c>
+      <c r="D437" t="n">
+        <v>314.14</v>
+      </c>
+      <c r="E437" t="n">
+        <v>315.08</v>
+      </c>
+      <c r="F437" t="n">
+        <v>319.25</v>
+      </c>
+      <c r="G437" t="n">
+        <v>322.17</v>
+      </c>
+      <c r="H437" t="n">
+        <v>332.1</v>
+      </c>
+      <c r="I437" t="n">
+        <v>339.1</v>
+      </c>
+      <c r="J437" t="n">
+        <v>337.93</v>
+      </c>
+      <c r="K437" t="n">
+        <v>329.58</v>
+      </c>
+      <c r="L437" t="n">
+        <v>325.2</v>
+      </c>
+      <c r="M437" t="n">
+        <v>327.63</v>
+      </c>
+      <c r="N437" t="n">
+        <v>341.08</v>
+      </c>
+      <c r="O437" t="n">
+        <v>356.33</v>
+      </c>
+      <c r="P437" t="n">
+        <v>344.41</v>
+      </c>
+      <c r="Q437" t="n">
+        <v>327.88</v>
+      </c>
+      <c r="R437" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:53:11+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>304.37</v>
+      </c>
+      <c r="C438" t="n">
+        <v>306.55</v>
+      </c>
+      <c r="D438" t="n">
+        <v>313.29</v>
+      </c>
+      <c r="E438" t="n">
+        <v>313.65</v>
+      </c>
+      <c r="F438" t="n">
+        <v>317.74</v>
+      </c>
+      <c r="G438" t="n">
+        <v>320.57</v>
+      </c>
+      <c r="H438" t="n">
+        <v>330.59</v>
+      </c>
+      <c r="I438" t="n">
+        <v>337.26</v>
+      </c>
+      <c r="J438" t="n">
+        <v>336.85</v>
+      </c>
+      <c r="K438" t="n">
+        <v>328.56</v>
+      </c>
+      <c r="L438" t="n">
+        <v>324.01</v>
+      </c>
+      <c r="M438" t="n">
+        <v>326.55</v>
+      </c>
+      <c r="N438" t="n">
+        <v>339.55</v>
+      </c>
+      <c r="O438" t="n">
+        <v>354.97</v>
+      </c>
+      <c r="P438" t="n">
+        <v>343.25</v>
+      </c>
+      <c r="Q438" t="n">
+        <v>327.32</v>
+      </c>
+      <c r="R438" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:52:47+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>303.86</v>
+      </c>
+      <c r="C439" t="n">
+        <v>305.38</v>
+      </c>
+      <c r="D439" t="n">
+        <v>312.37</v>
+      </c>
+      <c r="E439" t="n">
+        <v>313.68</v>
+      </c>
+      <c r="F439" t="n">
+        <v>317.44</v>
+      </c>
+      <c r="G439" t="n">
+        <v>320.78</v>
+      </c>
+      <c r="H439" t="n">
+        <v>330.14</v>
+      </c>
+      <c r="I439" t="n">
+        <v>337.07</v>
+      </c>
+      <c r="J439" t="n">
+        <v>336.96</v>
+      </c>
+      <c r="K439" t="n">
+        <v>327.97</v>
+      </c>
+      <c r="L439" t="n">
+        <v>324.06</v>
+      </c>
+      <c r="M439" t="n">
+        <v>325.97</v>
+      </c>
+      <c r="N439" t="n">
+        <v>339.12</v>
+      </c>
+      <c r="O439" t="n">
+        <v>354.66</v>
+      </c>
+      <c r="P439" t="n">
+        <v>343.11</v>
+      </c>
+      <c r="Q439" t="n">
+        <v>326.6</v>
+      </c>
+      <c r="R439" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-27 21:52:58+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>304.07</v>
+      </c>
+      <c r="C440" t="n">
+        <v>305.75</v>
+      </c>
+      <c r="D440" t="n">
+        <v>311.76</v>
+      </c>
+      <c r="E440" t="n">
+        <v>313.2</v>
+      </c>
+      <c r="F440" t="n">
+        <v>317.17</v>
+      </c>
+      <c r="G440" t="n">
+        <v>321.17</v>
+      </c>
+      <c r="H440" t="n">
+        <v>330.62</v>
+      </c>
+      <c r="I440" t="n">
+        <v>337.26</v>
+      </c>
+      <c r="J440" t="n">
+        <v>336.47</v>
+      </c>
+      <c r="K440" t="n">
+        <v>328.46</v>
+      </c>
+      <c r="L440" t="n">
+        <v>324.94</v>
+      </c>
+      <c r="M440" t="n">
+        <v>326.34</v>
+      </c>
+      <c r="N440" t="n">
+        <v>339.08</v>
+      </c>
+      <c r="O440" t="n">
+        <v>353.53</v>
+      </c>
+      <c r="P440" t="n">
+        <v>341.9</v>
+      </c>
+      <c r="Q440" t="n">
+        <v>326.06</v>
+      </c>
+      <c r="R440" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26608,7 +26848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B438"/>
+  <dimension ref="A1:B442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30991,6 +31231,46 @@
       </c>
       <c r="B438" t="n">
         <v>-0.27</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-05-27 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>-0.61</v>
       </c>
     </row>
   </sheetData>
@@ -31159,28 +31439,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.001729997660638269</v>
+        <v>-0.01606534639592662</v>
       </c>
       <c r="J2" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="K2" t="n">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="L2" t="n">
-        <v>2.001222368042122e-06</v>
+        <v>0.0001753263519952419</v>
       </c>
       <c r="M2" t="n">
-        <v>7.250102212825396</v>
+        <v>7.250655202210823</v>
       </c>
       <c r="N2" t="n">
-        <v>84.27428025602768</v>
+        <v>84.02823950175311</v>
       </c>
       <c r="O2" t="n">
-        <v>9.180102409887795</v>
+        <v>9.166691851576179</v>
       </c>
       <c r="P2" t="n">
-        <v>312.2673605248518</v>
+        <v>312.4139404441312</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31237,28 +31517,28 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07131970292764381</v>
+        <v>0.05835720075641852</v>
       </c>
       <c r="J3" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="K3" t="n">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005234592956678052</v>
+        <v>0.003560788389054492</v>
       </c>
       <c r="M3" t="n">
-        <v>5.826895976142956</v>
+        <v>5.835751485696086</v>
       </c>
       <c r="N3" t="n">
-        <v>54.46995880457965</v>
+        <v>54.40790088583659</v>
       </c>
       <c r="O3" t="n">
-        <v>7.380376603167324</v>
+        <v>7.376171153507529</v>
       </c>
       <c r="P3" t="n">
-        <v>311.5155169200516</v>
+        <v>311.6480665755284</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31315,28 +31595,28 @@
         <v>0.059</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2070149741226192</v>
+        <v>0.2010799974805572</v>
       </c>
       <c r="J4" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="K4" t="n">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06469622658872309</v>
+        <v>0.0623952413501575</v>
       </c>
       <c r="M4" t="n">
-        <v>4.810192979253646</v>
+        <v>4.795573980000161</v>
       </c>
       <c r="N4" t="n">
-        <v>34.76404930591296</v>
+        <v>34.54287514184841</v>
       </c>
       <c r="O4" t="n">
-        <v>5.896104587429988</v>
+        <v>5.877318703443638</v>
       </c>
       <c r="P4" t="n">
-        <v>310.5141606525762</v>
+        <v>310.5749443911922</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31393,28 +31673,28 @@
         <v>0.09429999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1404327161386431</v>
+        <v>0.1324778329076048</v>
       </c>
       <c r="J5" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="K5" t="n">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01932195947845849</v>
+        <v>0.01756244645296134</v>
       </c>
       <c r="M5" t="n">
-        <v>5.912723777836042</v>
+        <v>5.903276622870463</v>
       </c>
       <c r="N5" t="n">
-        <v>56.16489815003095</v>
+        <v>55.81600887125485</v>
       </c>
       <c r="O5" t="n">
-        <v>7.494324395836555</v>
+        <v>7.471011234849995</v>
       </c>
       <c r="P5" t="n">
-        <v>314.3860992834647</v>
+        <v>314.4675588128141</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31471,28 +31751,28 @@
         <v>0.0727</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1545776740389251</v>
+        <v>0.1414398462714805</v>
       </c>
       <c r="J6" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="K6" t="n">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02021534881401588</v>
+        <v>0.01724118806914698</v>
       </c>
       <c r="M6" t="n">
-        <v>5.909713423000301</v>
+        <v>5.936873262142757</v>
       </c>
       <c r="N6" t="n">
-        <v>64.98244218699155</v>
+        <v>64.82995428185042</v>
       </c>
       <c r="O6" t="n">
-        <v>8.06116878541763</v>
+        <v>8.051705054325476</v>
       </c>
       <c r="P6" t="n">
-        <v>320.7703011345554</v>
+        <v>320.9048291799055</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31549,28 +31829,28 @@
         <v>0.0653</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3170743031957979</v>
+        <v>0.2947341536589468</v>
       </c>
       <c r="J7" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="K7" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1003603196046333</v>
+        <v>0.08769771557769268</v>
       </c>
       <c r="M7" t="n">
-        <v>5.327233314979018</v>
+        <v>5.401173471100621</v>
       </c>
       <c r="N7" t="n">
-        <v>50.91788800939638</v>
+        <v>51.72850390753183</v>
       </c>
       <c r="O7" t="n">
-        <v>7.135677123398758</v>
+        <v>7.192253048074145</v>
       </c>
       <c r="P7" t="n">
-        <v>324.6784786540395</v>
+        <v>324.9060256076</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31627,28 +31907,28 @@
         <v>0.0597</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2879516296277057</v>
+        <v>0.2702805218096394</v>
       </c>
       <c r="J8" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="K8" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1022484935337651</v>
+        <v>0.09142392423074985</v>
       </c>
       <c r="M8" t="n">
-        <v>4.973568059653294</v>
+        <v>5.01698602968693</v>
       </c>
       <c r="N8" t="n">
-        <v>41.13201893512618</v>
+        <v>41.55750278243651</v>
       </c>
       <c r="O8" t="n">
-        <v>6.413424899001015</v>
+        <v>6.446510899892787</v>
       </c>
       <c r="P8" t="n">
-        <v>332.6411007214358</v>
+        <v>332.8210966378692</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31705,28 +31985,28 @@
         <v>0.0568</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1673620088310508</v>
+        <v>0.165061090263589</v>
       </c>
       <c r="J9" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="K9" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04018022279092781</v>
+        <v>0.03994871076904727</v>
       </c>
       <c r="M9" t="n">
-        <v>4.835292171400609</v>
+        <v>4.805957863089981</v>
       </c>
       <c r="N9" t="n">
-        <v>37.9648703082408</v>
+        <v>37.63724968665654</v>
       </c>
       <c r="O9" t="n">
-        <v>6.161563949862145</v>
+        <v>6.134920511845002</v>
       </c>
       <c r="P9" t="n">
-        <v>334.4249465858498</v>
+        <v>334.4483604864113</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31783,28 +32063,28 @@
         <v>0.0615</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1369820445491706</v>
+        <v>0.1415306621447845</v>
       </c>
       <c r="J10" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="K10" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02628982142315384</v>
+        <v>0.0285862137125098</v>
       </c>
       <c r="M10" t="n">
-        <v>4.809234596792265</v>
+        <v>4.786244497497263</v>
       </c>
       <c r="N10" t="n">
-        <v>39.43303176287553</v>
+        <v>39.12780612943492</v>
       </c>
       <c r="O10" t="n">
-        <v>6.279572578040287</v>
+        <v>6.255222308554262</v>
       </c>
       <c r="P10" t="n">
-        <v>330.9403417704066</v>
+        <v>330.8940891329586</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31861,28 +32141,28 @@
         <v>0.0587</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0264585326746369</v>
+        <v>0.03840470147115417</v>
       </c>
       <c r="J11" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="K11" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="L11" t="n">
-        <v>0.000733491631084382</v>
+        <v>0.001568010459466196</v>
       </c>
       <c r="M11" t="n">
-        <v>6.060465166730181</v>
+        <v>6.06363632429267</v>
       </c>
       <c r="N11" t="n">
-        <v>53.88394710077539</v>
+        <v>53.75969871021746</v>
       </c>
       <c r="O11" t="n">
-        <v>7.340568581572914</v>
+        <v>7.33210056601909</v>
       </c>
       <c r="P11" t="n">
-        <v>321.5181030797071</v>
+        <v>321.396436351715</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31939,28 +32219,28 @@
         <v>0.0634</v>
       </c>
       <c r="I12" t="n">
-        <v>0.04278601981471164</v>
+        <v>0.05691461852781345</v>
       </c>
       <c r="J12" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="K12" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="L12" t="n">
-        <v>0.00154305890034534</v>
+        <v>0.002767017872503885</v>
       </c>
       <c r="M12" t="n">
-        <v>6.677401310942303</v>
+        <v>6.6852954469962</v>
       </c>
       <c r="N12" t="n">
-        <v>66.92560928495691</v>
+        <v>66.82682610740898</v>
       </c>
       <c r="O12" t="n">
-        <v>8.180807373661654</v>
+        <v>8.174767648527325</v>
       </c>
       <c r="P12" t="n">
-        <v>315.817314918506</v>
+        <v>315.6734127004513</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32017,28 +32297,28 @@
         <v>0.0605</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.02720492547012166</v>
+        <v>-0.006764916318600635</v>
       </c>
       <c r="J13" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="K13" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0004463891199941727</v>
+        <v>2.791305088967189e-05</v>
       </c>
       <c r="M13" t="n">
-        <v>7.900695080300229</v>
+        <v>7.923778659467109</v>
       </c>
       <c r="N13" t="n">
-        <v>93.633076590847</v>
+        <v>93.84776505747112</v>
       </c>
       <c r="O13" t="n">
-        <v>9.676418582866649</v>
+        <v>9.687505615867849</v>
       </c>
       <c r="P13" t="n">
-        <v>316.3727289147178</v>
+        <v>316.1645510051556</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32095,28 +32375,28 @@
         <v>0.0692</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0326039031715686</v>
+        <v>0.05969587239600624</v>
       </c>
       <c r="J14" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="K14" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0007548274827403612</v>
+        <v>0.002522666631558756</v>
       </c>
       <c r="M14" t="n">
-        <v>6.946307793568896</v>
+        <v>7.012757663541049</v>
       </c>
       <c r="N14" t="n">
-        <v>79.50698141177853</v>
+        <v>80.65852701835415</v>
       </c>
       <c r="O14" t="n">
-        <v>8.916668739601047</v>
+        <v>8.981009242749623</v>
       </c>
       <c r="P14" t="n">
-        <v>324.2836399313517</v>
+        <v>324.0077141725764</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32173,28 +32453,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.09841983768837972</v>
+        <v>0.1323927701206023</v>
       </c>
       <c r="J15" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="K15" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="L15" t="n">
-        <v>0.005991529662255801</v>
+        <v>0.01068289062662642</v>
       </c>
       <c r="M15" t="n">
-        <v>7.499725236324117</v>
+        <v>7.592569244613962</v>
       </c>
       <c r="N15" t="n">
-        <v>90.7944666052091</v>
+        <v>92.91670131954621</v>
       </c>
       <c r="O15" t="n">
-        <v>9.528613047301748</v>
+        <v>9.63933095808761</v>
       </c>
       <c r="P15" t="n">
-        <v>333.9881902393545</v>
+        <v>333.6421847102712</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32251,28 +32531,28 @@
         <v>0.0862</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1043647624283057</v>
+        <v>0.141824376120236</v>
       </c>
       <c r="J16" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="K16" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="L16" t="n">
-        <v>0.006523611906771309</v>
+        <v>0.01179737057015895</v>
       </c>
       <c r="M16" t="n">
-        <v>7.566805267914352</v>
+        <v>7.668645590788175</v>
       </c>
       <c r="N16" t="n">
-        <v>93.71711955045544</v>
+        <v>96.44529689865796</v>
       </c>
       <c r="O16" t="n">
-        <v>9.680760277501733</v>
+        <v>9.820656642946945</v>
       </c>
       <c r="P16" t="n">
-        <v>320.2535913225785</v>
+        <v>319.8720708008781</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32329,28 +32609,28 @@
         <v>0.0844</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1960895305379514</v>
+        <v>0.2237407800677777</v>
       </c>
       <c r="J17" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="K17" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02571722341209748</v>
+        <v>0.03317759448393509</v>
       </c>
       <c r="M17" t="n">
-        <v>7.190516089936043</v>
+        <v>7.259016225534059</v>
       </c>
       <c r="N17" t="n">
-        <v>82.30220715529467</v>
+        <v>83.50464124432506</v>
       </c>
       <c r="O17" t="n">
-        <v>9.072056390658883</v>
+        <v>9.138087395310086</v>
       </c>
       <c r="P17" t="n">
-        <v>306.8633511864441</v>
+        <v>306.5817285490933</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32388,7 +32668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R436"/>
+  <dimension ref="A1:R440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72451,6 +72731,374 @@
         </is>
       </c>
     </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:53:28+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>-38.20573689168917,178.33372755046904</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>-38.20644085772017,178.33378475382645</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>-38.20714261578758,178.33388093060893</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>-38.20784748568449,178.33392188703445</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>-38.20855027591758,178.3339995448012</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>-38.20923533511498,178.33406331047578</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>-38.20992401779548,178.334103374485</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>-38.21063006549432,178.33410667123013</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>-38.21133285246565,178.3340169652411</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>-38.21202601486094,178.3338466848213</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>-38.212698656816066,178.33367847782702</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>-38.21337508444767,178.333498760063</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>-38.214085036217064,178.33343773205212</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>-38.21479977091245,178.3333916281117</t>
+        </is>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>-38.21550824096464,178.33341387083027</t>
+        </is>
+      </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>-38.216238184011196,178.3335160194315</t>
+        </is>
+      </c>
+      <c r="R437" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:53:11+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>-38.20573791839319,178.3337093710318</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>-38.20644200636459,178.33376441538698</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>-38.20714316124611,178.3338712725997</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>-38.20784840335117,178.33390563869847</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>-38.20855124494156,178.33398238730462</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>-38.20923552291108,178.33404508521676</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>-38.20992338980509,178.33408619119106</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>-38.21062928475526,178.33408573336297</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>-38.21133239420645,178.33400467550345</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>-38.21202534011472,178.33383509629192</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>-38.21269706086521,178.33366507273996</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>-38.21337316316355,178.33348669964343</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>-38.214082314408984,178.33342064628698</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>-38.21479985658347,178.33337613450462</t>
+        </is>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>-38.21551118288356,178.33340119221242</t>
+        </is>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>-38.21623991481904,178.3335100284693</t>
+        </is>
+      </c>
+      <c r="R438" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:52:47+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>-38.2057382456545,178.33370357633598</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>-38.2064427571526,178.3337511215461</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>-38.207143751623875,178.33386081922478</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>-38.20784838409943,178.33390597957265</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>-38.208551437462596,178.33397897853038</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>-38.209235498263006,178.33404747728204</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>-38.20992320265515,178.33408107034185</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>-38.210629204135245,178.3340835713006</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>-38.21133244088106,178.334005927236</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>-38.21202494981981,178.333828393123</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>-38.21269712792201,178.3336656359789</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>-38.213372131362284,178.33348022275163</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>-38.21408154945592,178.3334158444055</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>-38.21479987611113,178.33337260287354</t>
+        </is>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>-38.21551153794266,178.3333996620343</t>
+        </is>
+      </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>-38.21624214014299,178.33350232580318</t>
+        </is>
+      </c>
+      <c r="R439" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-27 21:52:58+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>-38.20573811089988,178.33370596238723</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>-38.206442519724085,178.33375532558128</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>-38.2071441430695,178.33385388818255</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>-38.207848692126916,178.3339005255856</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>-38.20855161073144,178.3339759106335</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>-38.20923545248788,178.33405191968896</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>-38.20992340228175,178.334086532581</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>-38.21062928475526,178.33408573336297</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>-38.21133223296678,178.33400035133653</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>-38.212025273963064,178.33383396016163</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>-38.21269830812104,178.33367554898442</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>-38.21337278958039,178.33348435456188</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>-38.21408147829747,178.33341539771882</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>-38.21479994729171,178.33335972950854</t>
+        </is>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>-38.215514606666886,178.33338643692292</t>
+        </is>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>-38.216243809135634,178.33349654880325</t>
+        </is>
+      </c>
+      <c r="R440" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0249/nzd0249.xlsx
+++ b/data/nzd0249/nzd0249.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R440"/>
+  <dimension ref="A1:R441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26832,6 +26832,66 @@
         <v>326.06</v>
       </c>
       <c r="R440" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:53:22+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>306.25</v>
+      </c>
+      <c r="C441" t="n">
+        <v>306.72</v>
+      </c>
+      <c r="D441" t="n">
+        <v>314.16</v>
+      </c>
+      <c r="E441" t="n">
+        <v>314.37</v>
+      </c>
+      <c r="F441" t="n">
+        <v>318.27</v>
+      </c>
+      <c r="G441" t="n">
+        <v>323.34</v>
+      </c>
+      <c r="H441" t="n">
+        <v>332.43</v>
+      </c>
+      <c r="I441" t="n">
+        <v>338.2</v>
+      </c>
+      <c r="J441" t="n">
+        <v>337</v>
+      </c>
+      <c r="K441" t="n">
+        <v>328.92</v>
+      </c>
+      <c r="L441" t="n">
+        <v>324.15</v>
+      </c>
+      <c r="M441" t="n">
+        <v>326.25</v>
+      </c>
+      <c r="N441" t="n">
+        <v>338.24</v>
+      </c>
+      <c r="O441" t="n">
+        <v>352.11</v>
+      </c>
+      <c r="P441" t="n">
+        <v>340.24</v>
+      </c>
+      <c r="Q441" t="n">
+        <v>324.68</v>
+      </c>
+      <c r="R441" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26848,7 +26908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B442"/>
+  <dimension ref="A1:B443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31271,6 +31331,16 @@
       </c>
       <c r="B442" t="n">
         <v>-0.61</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>-0.76</v>
       </c>
     </row>
   </sheetData>
@@ -31439,28 +31509,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01606534639592662</v>
+        <v>-0.01874796652860891</v>
       </c>
       <c r="J2" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K2" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001753263519952419</v>
+        <v>0.0002398548760921271</v>
       </c>
       <c r="M2" t="n">
-        <v>7.250655202210823</v>
+        <v>7.246516483265987</v>
       </c>
       <c r="N2" t="n">
-        <v>84.02823950175311</v>
+        <v>83.91070100868887</v>
       </c>
       <c r="O2" t="n">
-        <v>9.166691851576179</v>
+        <v>9.160278435107138</v>
       </c>
       <c r="P2" t="n">
-        <v>312.4139404441312</v>
+        <v>312.4414538171218</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31517,28 +31587,28 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05835720075641852</v>
+        <v>0.05532270612620103</v>
       </c>
       <c r="J3" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K3" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003560788389054492</v>
+        <v>0.003213211598017462</v>
       </c>
       <c r="M3" t="n">
-        <v>5.835751485696086</v>
+        <v>5.837016671906574</v>
       </c>
       <c r="N3" t="n">
-        <v>54.40790088583659</v>
+        <v>54.37903804574123</v>
       </c>
       <c r="O3" t="n">
-        <v>7.376171153507529</v>
+        <v>7.374214401937418</v>
       </c>
       <c r="P3" t="n">
-        <v>311.6480665755284</v>
+        <v>311.6791888285757</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31595,28 +31665,28 @@
         <v>0.059</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2010799974805572</v>
+        <v>0.2002300404670669</v>
       </c>
       <c r="J4" t="n">
+        <v>440</v>
+      </c>
+      <c r="K4" t="n">
         <v>439</v>
       </c>
-      <c r="K4" t="n">
-        <v>438</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.0623952413501575</v>
+        <v>0.06220936048077097</v>
       </c>
       <c r="M4" t="n">
-        <v>4.795573980000161</v>
+        <v>4.788848382657804</v>
       </c>
       <c r="N4" t="n">
-        <v>34.54287514184841</v>
+        <v>34.47165202891619</v>
       </c>
       <c r="O4" t="n">
-        <v>5.877318703443638</v>
+        <v>5.871256426772399</v>
       </c>
       <c r="P4" t="n">
-        <v>310.5749443911922</v>
+        <v>310.5836738819607</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31673,28 +31743,28 @@
         <v>0.09429999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1324778329076048</v>
+        <v>0.1307696838508014</v>
       </c>
       <c r="J5" t="n">
+        <v>440</v>
+      </c>
+      <c r="K5" t="n">
         <v>439</v>
       </c>
-      <c r="K5" t="n">
-        <v>438</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.01756244645296134</v>
+        <v>0.01720393060119574</v>
       </c>
       <c r="M5" t="n">
-        <v>5.903276622870463</v>
+        <v>5.899527740344775</v>
       </c>
       <c r="N5" t="n">
-        <v>55.81600887125485</v>
+        <v>55.71900425087372</v>
       </c>
       <c r="O5" t="n">
-        <v>7.471011234849995</v>
+        <v>7.464516344069033</v>
       </c>
       <c r="P5" t="n">
-        <v>314.4675588128141</v>
+        <v>314.4851023722956</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31751,28 +31821,28 @@
         <v>0.0727</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1414398462714805</v>
+        <v>0.1384326373587678</v>
       </c>
       <c r="J6" t="n">
+        <v>440</v>
+      </c>
+      <c r="K6" t="n">
         <v>439</v>
       </c>
-      <c r="K6" t="n">
-        <v>438</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.01724118806914698</v>
+        <v>0.0165940066289173</v>
       </c>
       <c r="M6" t="n">
-        <v>5.936873262142757</v>
+        <v>5.941909684754099</v>
       </c>
       <c r="N6" t="n">
-        <v>64.82995428185042</v>
+        <v>64.77568995767382</v>
       </c>
       <c r="O6" t="n">
-        <v>8.051705054325476</v>
+        <v>8.048334607710704</v>
       </c>
       <c r="P6" t="n">
-        <v>320.9048291799055</v>
+        <v>320.9357147447357</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31829,28 +31899,28 @@
         <v>0.0653</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2947341536589468</v>
+        <v>0.2903262479983024</v>
       </c>
       <c r="J7" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K7" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08769771557769268</v>
+        <v>0.08543880024077177</v>
       </c>
       <c r="M7" t="n">
-        <v>5.401173471100621</v>
+        <v>5.41309440292139</v>
       </c>
       <c r="N7" t="n">
-        <v>51.72850390753183</v>
+        <v>51.81366629393477</v>
       </c>
       <c r="O7" t="n">
-        <v>7.192253048074145</v>
+        <v>7.198171038113416</v>
       </c>
       <c r="P7" t="n">
-        <v>324.9060256076</v>
+        <v>324.9510618437674</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31907,28 +31977,28 @@
         <v>0.0597</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2702805218096394</v>
+        <v>0.2667249005984082</v>
       </c>
       <c r="J8" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K8" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09142392423074985</v>
+        <v>0.0894357315038129</v>
       </c>
       <c r="M8" t="n">
-        <v>5.01698602968693</v>
+        <v>5.023671255451468</v>
       </c>
       <c r="N8" t="n">
-        <v>41.55750278243651</v>
+        <v>41.59496410316797</v>
       </c>
       <c r="O8" t="n">
-        <v>6.446510899892787</v>
+        <v>6.449415795494036</v>
       </c>
       <c r="P8" t="n">
-        <v>332.8210966378692</v>
+        <v>332.8574249554239</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31985,28 +32055,28 @@
         <v>0.0568</v>
       </c>
       <c r="I9" t="n">
-        <v>0.165061090263589</v>
+        <v>0.1647432204395158</v>
       </c>
       <c r="J9" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K9" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03994871076904727</v>
+        <v>0.04001004472177561</v>
       </c>
       <c r="M9" t="n">
-        <v>4.805957863089981</v>
+        <v>4.796914173179482</v>
       </c>
       <c r="N9" t="n">
-        <v>37.63724968665654</v>
+        <v>37.55237995680994</v>
       </c>
       <c r="O9" t="n">
-        <v>6.134920511845002</v>
+        <v>6.127999670105241</v>
       </c>
       <c r="P9" t="n">
-        <v>334.4483604864113</v>
+        <v>334.4516035801022</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32063,28 +32133,28 @@
         <v>0.0615</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1415306621447845</v>
+        <v>0.1425996307086948</v>
       </c>
       <c r="J10" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K10" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0285862137125098</v>
+        <v>0.02915318773006492</v>
       </c>
       <c r="M10" t="n">
-        <v>4.786244497497263</v>
+        <v>4.78024229195125</v>
       </c>
       <c r="N10" t="n">
-        <v>39.12780612943492</v>
+        <v>39.05046169692864</v>
       </c>
       <c r="O10" t="n">
-        <v>6.255222308554262</v>
+        <v>6.249036861543436</v>
       </c>
       <c r="P10" t="n">
-        <v>330.8940891329586</v>
+        <v>330.8831828910227</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32141,28 +32211,28 @@
         <v>0.0587</v>
       </c>
       <c r="I11" t="n">
-        <v>0.03840470147115417</v>
+        <v>0.04142183520354092</v>
       </c>
       <c r="J11" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K11" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001568010459466196</v>
+        <v>0.001830375005511642</v>
       </c>
       <c r="M11" t="n">
-        <v>6.06363632429267</v>
+        <v>6.064573020360192</v>
       </c>
       <c r="N11" t="n">
-        <v>53.75969871021746</v>
+        <v>53.73249852311392</v>
       </c>
       <c r="O11" t="n">
-        <v>7.33210056601909</v>
+        <v>7.330245461313961</v>
       </c>
       <c r="P11" t="n">
-        <v>321.396436351715</v>
+        <v>321.3656098418526</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32219,28 +32289,28 @@
         <v>0.0634</v>
       </c>
       <c r="I12" t="n">
-        <v>0.05691461852781345</v>
+        <v>0.06014659228230709</v>
       </c>
       <c r="J12" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K12" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L12" t="n">
-        <v>0.002767017872503885</v>
+        <v>0.00310109627560462</v>
       </c>
       <c r="M12" t="n">
-        <v>6.6852954469962</v>
+        <v>6.685728231311039</v>
       </c>
       <c r="N12" t="n">
-        <v>66.82682610740898</v>
+        <v>66.78393604610972</v>
       </c>
       <c r="O12" t="n">
-        <v>8.174767648527325</v>
+        <v>8.172143907574664</v>
       </c>
       <c r="P12" t="n">
-        <v>315.6734127004513</v>
+        <v>315.6403911377183</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32297,28 +32367,28 @@
         <v>0.0605</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.006764916318600635</v>
+        <v>-0.001991689374484729</v>
       </c>
       <c r="J13" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K13" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L13" t="n">
-        <v>2.791305088967189e-05</v>
+        <v>2.426717723436056e-06</v>
       </c>
       <c r="M13" t="n">
-        <v>7.923778659467109</v>
+        <v>7.928066736685431</v>
       </c>
       <c r="N13" t="n">
-        <v>93.84776505747112</v>
+        <v>93.8721978663409</v>
       </c>
       <c r="O13" t="n">
-        <v>9.687505615867849</v>
+        <v>9.688766581270338</v>
       </c>
       <c r="P13" t="n">
-        <v>316.1645510051556</v>
+        <v>316.1157822264009</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32375,28 +32445,28 @@
         <v>0.0692</v>
       </c>
       <c r="I14" t="n">
-        <v>0.05969587239600624</v>
+        <v>0.06556644095631271</v>
       </c>
       <c r="J14" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K14" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L14" t="n">
-        <v>0.002522666631558756</v>
+        <v>0.003044770653071072</v>
       </c>
       <c r="M14" t="n">
-        <v>7.012757663541049</v>
+        <v>7.02580671025957</v>
       </c>
       <c r="N14" t="n">
-        <v>80.65852701835415</v>
+        <v>80.83480226248635</v>
       </c>
       <c r="O14" t="n">
-        <v>8.981009242749623</v>
+        <v>8.990817663732612</v>
       </c>
       <c r="P14" t="n">
-        <v>324.0077141725764</v>
+        <v>323.9477336892189</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32453,28 +32523,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1323927701206023</v>
+        <v>0.1393244848922367</v>
       </c>
       <c r="J15" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K15" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01068289062662642</v>
+        <v>0.01181837765317884</v>
       </c>
       <c r="M15" t="n">
-        <v>7.592569244613962</v>
+        <v>7.609040105818534</v>
       </c>
       <c r="N15" t="n">
-        <v>92.91670131954621</v>
+        <v>93.20686282258373</v>
       </c>
       <c r="O15" t="n">
-        <v>9.63933095808761</v>
+        <v>9.654370141163209</v>
       </c>
       <c r="P15" t="n">
-        <v>333.6421847102712</v>
+        <v>333.5713623362155</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32531,28 +32601,28 @@
         <v>0.0862</v>
       </c>
       <c r="I16" t="n">
-        <v>0.141824376120236</v>
+        <v>0.1495229865827722</v>
       </c>
       <c r="J16" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K16" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01179737057015895</v>
+        <v>0.01308384177656641</v>
       </c>
       <c r="M16" t="n">
-        <v>7.668645590788175</v>
+        <v>7.687448184048474</v>
       </c>
       <c r="N16" t="n">
-        <v>96.44529689865796</v>
+        <v>96.84450671824015</v>
       </c>
       <c r="O16" t="n">
-        <v>9.820656642946945</v>
+        <v>9.840960660333938</v>
       </c>
       <c r="P16" t="n">
-        <v>319.8720708008781</v>
+        <v>319.7934129380188</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32609,28 +32679,28 @@
         <v>0.0844</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2237407800677777</v>
+        <v>0.2293636833890716</v>
       </c>
       <c r="J17" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K17" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03317759448393509</v>
+        <v>0.03485904370543946</v>
       </c>
       <c r="M17" t="n">
-        <v>7.259016225534059</v>
+        <v>7.269942971072354</v>
       </c>
       <c r="N17" t="n">
-        <v>83.50464124432506</v>
+        <v>83.64474755359124</v>
       </c>
       <c r="O17" t="n">
-        <v>9.138087395310086</v>
+        <v>9.145750245528863</v>
       </c>
       <c r="P17" t="n">
-        <v>306.5817285490933</v>
+        <v>306.5242784987929</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32668,7 +32738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R440"/>
+  <dimension ref="A1:R441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73099,6 +73169,98 @@
         </is>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:53:22+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>-38.2057367120157,178.33373073187047</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>-38.2064418972756,178.33376634697066</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>-38.207142602953255,178.3338811578562</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>-38.20784794130948,178.33391381967888</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>-38.20855090482085,178.33398840947237</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>-38.20923519778728,178.33407663769617</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>-38.20992415503807,178.3341071297744</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>-38.21062968361156,178.33409642988207</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>-38.211332457853636,178.33400638241147</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>-38.21202557826058,178.33383918636113</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>-38.21269724862422,178.333666649809</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>-38.21337262947328,178.33348334952697</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>-38.21407998396993,178.33340601729935</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>-38.21480003673786,178.3333435523593</t>
+        </is>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>-38.21551881664988,178.33336829337958</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>-38.216248074337855,178.33348178535763</t>
+        </is>
+      </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
